--- a/releases/SNPS_ANSS_merger_model.xlsx
+++ b/releases/SNPS_ANSS_merger_model.xlsx
@@ -635,12 +635,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Expected close</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>2025-07-17</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="B7" s="4">
         <f>'Deal &amp; S&amp;U'!B6</f>
-        <v/>
+        <v>34063247846.462196</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
       </c>
       <c r="B8" s="5">
         <f>'Deal &amp; S&amp;U'!B9</f>
-        <v/>
+        <v>0.2870635967805777</v>
       </c>
     </row>
     <row r="9">
@@ -681,7 +681,7 @@
       </c>
       <c r="B9" s="4">
         <f>'PPA'!B11</f>
-        <v/>
+        <v>25435888846.462196</v>
       </c>
     </row>
     <row r="11">
@@ -699,7 +699,7 @@
       </c>
       <c r="B12" s="5">
         <f>'Accretion-Dilution'!B6</f>
-        <v/>
+        <v>-0.38539521530334186</v>
       </c>
     </row>
     <row r="13">
@@ -710,7 +710,7 @@
       </c>
       <c r="B13" s="5">
         <f>'Accretion-Dilution'!C6</f>
-        <v/>
+        <v>-0.31427713326459683</v>
       </c>
     </row>
     <row r="14">
@@ -721,7 +721,7 @@
       </c>
       <c r="B14" s="5">
         <f>'Accretion-Dilution'!D6</f>
-        <v/>
+        <v>-0.2563615473345586</v>
       </c>
     </row>
     <row r="16">
@@ -856,7 +856,7 @@
       </c>
       <c r="B13" s="13">
         <f>'Deal &amp; S&amp;U'!B8</f>
-        <v/>
+        <v>30118493.444999997</v>
       </c>
     </row>
     <row r="14">
@@ -867,7 +867,7 @@
       </c>
       <c r="B14" s="5">
         <f>B12/(B12+B13)</f>
-        <v/>
+        <v>0.838127002990514</v>
       </c>
     </row>
     <row r="15">
@@ -878,7 +878,7 @@
       </c>
       <c r="B15" s="5">
         <f>B13/(B12+B13)</f>
-        <v/>
+        <v>0.161872997009486</v>
       </c>
     </row>
   </sheetData>
@@ -958,15 +958,15 @@
       </c>
       <c r="D7" s="5">
         <f>B7+(C7-B7)/(C6-B6)*(D6-B6)</f>
-        <v/>
+        <v>1.0514083427398488</v>
       </c>
       <c r="E7" s="5">
         <f>B7+(C7-B7)/(C6-B6)*(E6-B6)</f>
-        <v/>
+        <v>1.7527089127742648</v>
       </c>
       <c r="F7" s="5">
         <f>B7+(C7-B7)/(C6-B6)*(F6-B6)</f>
-        <v/>
+        <v>2.4540094828086807</v>
       </c>
     </row>
     <row r="8">
@@ -981,15 +981,15 @@
       </c>
       <c r="D8" s="5">
         <f>B8+(C8-B8)/(C6-B6)*(D6-B6)</f>
-        <v/>
+        <v>1.005007032051509</v>
       </c>
       <c r="E8" s="5">
         <f>B8+(C8-B8)/(C6-B6)*(E6-B6)</f>
-        <v/>
+        <v>1.706307602085925</v>
       </c>
       <c r="F8" s="5">
         <f>B8+(C8-B8)/(C6-B6)*(F6-B6)</f>
-        <v/>
+        <v>2.407608172120341</v>
       </c>
     </row>
     <row r="9">
@@ -1004,15 +1004,15 @@
       </c>
       <c r="D9" s="5">
         <f>B9+(C9-B9)/(C6-B6)*(D6-B6)</f>
-        <v/>
+        <v>0.9586057213631678</v>
       </c>
       <c r="E9" s="5">
         <f>B9+(C9-B9)/(C6-B6)*(E6-B6)</f>
-        <v/>
+        <v>1.6599062913975837</v>
       </c>
       <c r="F9" s="5">
         <f>B9+(C9-B9)/(C6-B6)*(F6-B6)</f>
-        <v/>
+        <v>2.3612068614319996</v>
       </c>
     </row>
     <row r="10">
@@ -1027,15 +1027,15 @@
       </c>
       <c r="D10" s="5">
         <f>B10+(C10-B10)/(C6-B6)*(D6-B6)</f>
-        <v/>
+        <v>0.912204410674829</v>
       </c>
       <c r="E10" s="5">
         <f>B10+(C10-B10)/(C6-B6)*(E6-B6)</f>
-        <v/>
+        <v>1.6135049807092459</v>
       </c>
       <c r="F10" s="5">
         <f>B10+(C10-B10)/(C6-B6)*(F6-B6)</f>
-        <v/>
+        <v>2.314805550743663</v>
       </c>
     </row>
     <row r="11">
@@ -1050,15 +1050,15 @@
       </c>
       <c r="D11" s="5">
         <f>B11+(C11-B11)/(C6-B6)*(D6-B6)</f>
-        <v/>
+        <v>0.8658030999864871</v>
       </c>
       <c r="E11" s="5">
         <f>B11+(C11-B11)/(C6-B6)*(E6-B6)</f>
-        <v/>
+        <v>1.5671036700209027</v>
       </c>
       <c r="F11" s="5">
         <f>B11+(C11-B11)/(C6-B6)*(F6-B6)</f>
-        <v/>
+        <v>2.268404240055319</v>
       </c>
     </row>
   </sheetData>
@@ -1497,15 +1497,15 @@
       </c>
       <c r="G4" s="12">
         <f>(C4+D4)/2</f>
-        <v/>
+        <v>328.145</v>
       </c>
       <c r="H4" s="12">
         <f>(E4+F4)/2</f>
-        <v/>
+        <v>448.7305633171268</v>
       </c>
       <c r="I4" s="5">
         <f>MAX(0,MIN(1,(MIN(D4,F4)-MAX(C4,E4))/(D4-C4)))</f>
-        <v/>
+        <v>0.4574337740521195</v>
       </c>
     </row>
     <row r="5">
@@ -1533,15 +1533,15 @@
       </c>
       <c r="G5" s="12">
         <f>(C5+D5)/2</f>
-        <v/>
+        <v>269.515</v>
       </c>
       <c r="H5" s="12">
         <f>(E5+F5)/2</f>
-        <v/>
+        <v>295.9622637260368</v>
       </c>
       <c r="I5" s="5">
         <f>MAX(0,MIN(1,(MIN(D5,F5)-MAX(C5,E5))/(D5-C5)))</f>
-        <v/>
+        <v>0.7939231702418772</v>
       </c>
     </row>
     <row r="6">
@@ -1569,15 +1569,15 @@
       </c>
       <c r="G6" s="12">
         <f>(C6+D6)/2</f>
-        <v/>
+        <v>259.925</v>
       </c>
       <c r="H6" s="12">
         <f>(E6+F6)/2</f>
-        <v/>
+        <v>295.9622637260368</v>
       </c>
       <c r="I6" s="5">
         <f>MAX(0,MIN(1,(MIN(D6,F6)-MAX(C6,E6))/(D6-C6)))</f>
-        <v/>
+        <v>0.7690494555144768</v>
       </c>
     </row>
   </sheetData>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="B27" s="9" t="n">
-        <v>8918797000</v>
+        <v>6085487000</v>
       </c>
     </row>
     <row r="28">
@@ -1963,23 +1963,23 @@
       </c>
       <c r="C4" s="4">
         <f>B4*(1+'Assumptions'!B4)</f>
-        <v/>
+        <v>6801453960.000001</v>
       </c>
       <c r="D4" s="4">
         <f>C4*(1+'Assumptions'!C4)</f>
-        <v/>
+        <v>7481599356.000002</v>
       </c>
       <c r="E4" s="4">
         <f>D4*(1+'Assumptions'!D4)</f>
-        <v/>
+        <v>8229759291.600002</v>
       </c>
       <c r="F4" s="4">
         <f>E4*(1+'Assumptions'!E4)</f>
-        <v/>
+        <v>8970437627.844004</v>
       </c>
       <c r="G4" s="4">
         <f>F4*(1+'Assumptions'!F4)</f>
-        <v/>
+        <v>9777777014.349964</v>
       </c>
     </row>
     <row r="5">
@@ -2085,23 +2085,23 @@
       </c>
       <c r="C4" s="4">
         <f>B4*(1+'Assumptions'!B5)</f>
-        <v/>
+        <v>2773841810.0</v>
       </c>
       <c r="D4" s="4">
         <f>C4*(1+'Assumptions'!C5)</f>
-        <v/>
+        <v>2995749154.8</v>
       </c>
       <c r="E4" s="4">
         <f>D4*(1+'Assumptions'!D5)</f>
-        <v/>
+        <v>3235409087.1840005</v>
       </c>
       <c r="F4" s="4">
         <f>E4*(1+'Assumptions'!E5)</f>
-        <v/>
+        <v>3461887723.2868805</v>
       </c>
       <c r="G4" s="4">
         <f>F4*(1+'Assumptions'!F5)</f>
-        <v/>
+        <v>3704219863.916962</v>
       </c>
     </row>
     <row r="5">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="B4" s="4">
         <f>'Assumptions'!B8*'Assumptions'!B11</f>
-        <v/>
+        <v>17198096257.0</v>
       </c>
     </row>
     <row r="5">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="B5" s="4">
         <f>'Assumptions'!B9*'Assumptions'!B10*'Assumptions'!B11</f>
-        <v/>
+        <v>16865151589.462198</v>
       </c>
     </row>
     <row r="6">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="B6" s="4">
         <f>B4+B5</f>
-        <v/>
+        <v>34063247846.462196</v>
       </c>
     </row>
     <row r="7">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="B7" s="12">
         <f>'Assumptions'!B8+'Assumptions'!B9*'Assumptions'!B10</f>
-        <v/>
+        <v>390.1862</v>
       </c>
     </row>
     <row r="8">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="B8" s="13">
         <f>'Assumptions'!B9*'Assumptions'!B11</f>
-        <v/>
+        <v>30118493.444999997</v>
       </c>
     </row>
     <row r="9">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="B9" s="5">
         <f>B7/'Assumptions'!B12-1</f>
-        <v/>
+        <v>0.2870635967805777</v>
       </c>
     </row>
     <row r="11">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="B16" s="4">
         <f>SUM(B12:B15)</f>
-        <v/>
+        <v>34213247846.4622</v>
       </c>
     </row>
     <row r="18">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="B23" s="4">
         <f>SUM(B19:B22)</f>
-        <v/>
+        <v>34213247846.4622</v>
       </c>
     </row>
   </sheetData>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="B3" s="4">
         <f>'Deal &amp; S&amp;U'!B6</f>
-        <v/>
+        <v>34063247846.462196</v>
       </c>
     </row>
     <row r="4">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="B4" s="4">
         <f>'Assumptions'!B27</f>
-        <v/>
+        <v>6085487000.0</v>
       </c>
     </row>
     <row r="5">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="B5" s="4">
         <f>'Assumptions'!B28</f>
-        <v/>
+        <v>3778128000.0</v>
       </c>
     </row>
     <row r="6">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="B6" s="4">
         <f>B4-B5</f>
-        <v/>
+        <v>2307359000.0</v>
       </c>
     </row>
     <row r="7">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="B7" s="4">
         <f>'Assumptions'!B21</f>
-        <v/>
+        <v>8000000000.0</v>
       </c>
     </row>
     <row r="8">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="B8" s="4">
         <f>'Assumptions'!B22</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="9">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="B9" s="4">
         <f>(B7+B8)*'Assumptions'!B23</f>
-        <v/>
+        <v>1680000000.0</v>
       </c>
     </row>
     <row r="10">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="B10" s="4">
         <f>B6+B7+B8-B9</f>
-        <v/>
+        <v>8627359000.0</v>
       </c>
     </row>
     <row r="11">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="B11" s="4">
         <f>B3-B10</f>
-        <v/>
+        <v>25435888846.462196</v>
       </c>
     </row>
   </sheetData>
@@ -2685,23 +2685,23 @@
       </c>
       <c r="B10" s="4">
         <f>B4+B5-B6-B7-B8+B9</f>
-        <v/>
+        <v>1472315983.2020597</v>
       </c>
       <c r="C10" s="4">
         <f>C4+C5-C6-C7-C8+C9</f>
-        <v/>
+        <v>1840310245.479661</v>
       </c>
       <c r="D10" s="4">
         <f>D4+D5-D6-D7-D8+D9</f>
-        <v/>
+        <v>2232777280.2923913</v>
       </c>
       <c r="E10" s="4">
         <f>E4+E5-E6-E7-E8+E9</f>
-        <v/>
+        <v>2564008598.976114</v>
       </c>
       <c r="F10" s="4">
         <f>F4+F5-F6-F7-F8+F9</f>
-        <v/>
+        <v>2925280518.6038523</v>
       </c>
     </row>
     <row r="11">
@@ -2734,23 +2734,23 @@
       </c>
       <c r="B12" s="13">
         <f>'Deal &amp; S&amp;U'!B8</f>
-        <v/>
+        <v>30118493.444999997</v>
       </c>
       <c r="C12" s="13">
         <f>'Deal &amp; S&amp;U'!B8</f>
-        <v/>
+        <v>30118493.444999997</v>
       </c>
       <c r="D12" s="13">
         <f>'Deal &amp; S&amp;U'!B8</f>
-        <v/>
+        <v>30118493.444999997</v>
       </c>
       <c r="E12" s="13">
         <f>'Deal &amp; S&amp;U'!B8</f>
-        <v/>
+        <v>30118493.444999997</v>
       </c>
       <c r="F12" s="13">
         <f>'Deal &amp; S&amp;U'!B8</f>
-        <v/>
+        <v>30118493.444999997</v>
       </c>
     </row>
     <row r="13">
@@ -2761,23 +2761,23 @@
       </c>
       <c r="B13" s="13">
         <f>B11+B12</f>
-        <v/>
+        <v>186062493.445</v>
       </c>
       <c r="C13" s="13">
         <f>C11+C12</f>
-        <v/>
+        <v>186062493.445</v>
       </c>
       <c r="D13" s="13">
         <f>D11+D12</f>
-        <v/>
+        <v>186062493.445</v>
       </c>
       <c r="E13" s="13">
         <f>E11+E12</f>
-        <v/>
+        <v>186062493.445</v>
       </c>
       <c r="F13" s="13">
         <f>F11+F12</f>
-        <v/>
+        <v>186062493.445</v>
       </c>
     </row>
     <row r="14">
@@ -2788,23 +2788,23 @@
       </c>
       <c r="B14" s="12">
         <f>B10/B13</f>
-        <v/>
+        <v>7.913018663470055</v>
       </c>
       <c r="C14" s="12">
         <f>C10/C13</f>
-        <v/>
+        <v>9.890817925772106</v>
       </c>
       <c r="D14" s="12">
         <f>D10/D13</f>
-        <v/>
+        <v>12.000147041737884</v>
       </c>
       <c r="E14" s="12">
         <f>E10/E13</f>
-        <v/>
+        <v>13.780362455123358</v>
       </c>
       <c r="F14" s="12">
         <f>F10/F13</f>
-        <v/>
+        <v>15.72203222928733</v>
       </c>
     </row>
   </sheetData>
@@ -2901,19 +2901,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>26051428846.4622</v>
+        <v>28884738846.4622</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>26051428846.4622</v>
+        <v>28884738846.4622</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>26051428846.4622</v>
+        <v>28884738846.4622</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>26051428846.4622</v>
+        <v>28884738846.4622</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>26051428846.4622</v>
+        <v>28884738846.4622</v>
       </c>
     </row>
     <row r="6">
@@ -2923,19 +2923,19 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>45341886330.08261</v>
+        <v>48175196330.08261</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>47604398267.88045</v>
+        <v>50437708267.88045</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>50135343087.54243</v>
+        <v>52968653087.54243</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>52938063220.65936</v>
+        <v>55771373220.65936</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>56039856269.37791</v>
+        <v>58873166269.37791</v>
       </c>
     </row>
     <row r="7">
@@ -2945,19 +2945,19 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>15578259292.41918</v>
+        <v>20463109292.41918</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>15591446050.26531</v>
+        <v>20476296050.26532</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>15605911358.1844</v>
+        <v>20490761358.1844</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>15620134507.54496</v>
+        <v>20504984507.54496</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>15635596788.04665</v>
+        <v>20520446788.04665</v>
       </c>
     </row>
     <row r="8">
@@ -2967,19 +2967,19 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>29763627037.66344</v>
+        <v>27712087037.66344</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>32012952217.61514</v>
+        <v>29961412217.61514</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>34529431729.35803</v>
+        <v>32477891729.35803</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>37317928713.1144</v>
+        <v>35266388713.1144</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>40404259481.33126</v>
+        <v>38352719481.33126</v>
       </c>
     </row>
   </sheetData>
@@ -3055,23 +3055,23 @@
       </c>
       <c r="B4" s="12">
         <f>'Pro Forma IS'!B4/'Pro Forma IS'!B11</f>
-        <v/>
+        <v>12.874970811324829</v>
       </c>
       <c r="C4" s="12">
         <f>'Pro Forma IS'!C4/'Pro Forma IS'!C11</f>
-        <v/>
+        <v>14.423928974193933</v>
       </c>
       <c r="D4" s="12">
         <f>'Pro Forma IS'!D4/'Pro Forma IS'!D11</f>
-        <v/>
+        <v>16.13707171640394</v>
       </c>
       <c r="E4" s="12">
         <f>'Pro Forma IS'!E4/'Pro Forma IS'!E11</f>
-        <v/>
+        <v>17.88139962907436</v>
       </c>
       <c r="F4" s="12">
         <f>'Pro Forma IS'!F4/'Pro Forma IS'!F11</f>
-        <v/>
+        <v>19.79127615180359</v>
       </c>
     </row>
     <row r="5">
@@ -3082,23 +3082,23 @@
       </c>
       <c r="B5" s="12">
         <f>'Pro Forma IS'!B14</f>
-        <v/>
+        <v>7.913018663470055</v>
       </c>
       <c r="C5" s="12">
         <f>'Pro Forma IS'!C14</f>
-        <v/>
+        <v>9.890817925772106</v>
       </c>
       <c r="D5" s="12">
         <f>'Pro Forma IS'!D14</f>
-        <v/>
+        <v>12.000147041737884</v>
       </c>
       <c r="E5" s="12">
         <f>'Pro Forma IS'!E14</f>
-        <v/>
+        <v>13.780362455123358</v>
       </c>
       <c r="F5" s="12">
         <f>'Pro Forma IS'!F14</f>
-        <v/>
+        <v>15.72203222928733</v>
       </c>
     </row>
     <row r="6">
@@ -3109,23 +3109,23 @@
       </c>
       <c r="B6" s="5">
         <f>B5/B4-1</f>
-        <v/>
+        <v>-0.38539521530334186</v>
       </c>
       <c r="C6" s="5">
         <f>C5/C4-1</f>
-        <v/>
+        <v>-0.31427713326459683</v>
       </c>
       <c r="D6" s="5">
         <f>D5/D4-1</f>
-        <v/>
+        <v>-0.2563615473345586</v>
       </c>
       <c r="E6" s="5">
         <f>E5/E4-1</f>
-        <v/>
+        <v>-0.22934654216233152</v>
       </c>
       <c r="F6" s="5">
         <f>F5/F4-1</f>
-        <v/>
+        <v>-0.2056079603611326</v>
       </c>
     </row>
   </sheetData>
